--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_10.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4565 +469,4350 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:36.155</t>
+          <t>2026-05-29 09:38:01.999</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421837835</v>
+        <v>1780022278206</v>
       </c>
       <c r="C2" t="n">
-        <v>86299</v>
+        <v>83624</v>
       </c>
       <c r="D2" t="n">
-        <v>95.26000000000001</v>
+        <v>-629.66</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>705</v>
+        <v>3259</v>
       </c>
       <c r="G2" t="n">
-        <v>62.22</v>
+        <v>263.94</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3792</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.956</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:36.156</t>
+          <t>2026-05-29 09:38:02.001</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421838037</v>
+        <v>1780022278406</v>
       </c>
       <c r="C3" t="n">
-        <v>86512</v>
+        <v>83856</v>
       </c>
       <c r="D3" t="n">
-        <v>303.49</v>
+        <v>-366.18</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>705</v>
+        <v>540</v>
       </c>
       <c r="G3" t="n">
-        <v>62.54</v>
+        <v>300.59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3594</v>
+      </c>
+      <c r="L3" t="n">
+        <v>105</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:36.156</t>
+          <t>2026-05-29 09:38:02.003</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421838238</v>
+        <v>1780022278645</v>
       </c>
       <c r="C4" t="n">
-        <v>85989</v>
+        <v>83451</v>
       </c>
       <c r="D4" t="n">
-        <v>-234.68</v>
+        <v>-752.87</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>705</v>
+        <v>540</v>
       </c>
       <c r="G4" t="n">
-        <v>62.54</v>
+        <v>300.59</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3357</v>
+      </c>
+      <c r="L4" t="n">
+        <v>110</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:36.565</t>
+          <t>2026-05-29 09:38:02.004</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421838440</v>
+        <v>1780022278845</v>
       </c>
       <c r="C5" t="n">
-        <v>86158</v>
+        <v>83560</v>
       </c>
       <c r="D5" t="n">
-        <v>-53.95</v>
+        <v>-606.23</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>705</v>
+        <v>540</v>
       </c>
       <c r="G5" t="n">
-        <v>62.54</v>
+        <v>300.59</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3158</v>
+      </c>
+      <c r="L5" t="n">
+        <v>111</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:36.566</t>
+          <t>2026-05-29 09:38:02.005</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421838641</v>
+        <v>1780022279045</v>
       </c>
       <c r="C6" t="n">
-        <v>86304</v>
+        <v>83921</v>
       </c>
       <c r="D6" t="n">
-        <v>94.75</v>
+        <v>-214.91</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
-        <v>705</v>
+        <v>540</v>
       </c>
       <c r="G6" t="n">
-        <v>62.54</v>
+        <v>300.59</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2960</v>
+      </c>
+      <c r="L6" t="n">
+        <v>108</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:36.952</t>
+          <t>2026-05-29 09:38:02.108</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421838842</v>
+        <v>1780022279245</v>
       </c>
       <c r="C7" t="n">
-        <v>86509</v>
+        <v>83782</v>
       </c>
       <c r="D7" t="n">
-        <v>295.01</v>
+        <v>-343.17</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>786</v>
+        <v>699</v>
       </c>
       <c r="G7" t="n">
-        <v>54.51</v>
+        <v>311.57</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2862</v>
+      </c>
+      <c r="L7" t="n">
+        <v>105</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:36.955</t>
+          <t>2026-05-29 09:38:02.109</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421839044</v>
+        <v>1780022279445</v>
       </c>
       <c r="C8" t="n">
-        <v>85934</v>
+        <v>84993</v>
       </c>
       <c r="D8" t="n">
-        <v>-294.74</v>
+        <v>884.99</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>786</v>
+        <v>699</v>
       </c>
       <c r="G8" t="n">
-        <v>54.51</v>
+        <v>311.57</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2664</v>
+      </c>
+      <c r="L8" t="n">
+        <v>115</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.758</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:37.394</t>
+          <t>2026-05-29 09:38:02.111</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421839245</v>
+        <v>1780022279646</v>
       </c>
       <c r="C9" t="n">
-        <v>86087</v>
+        <v>85244</v>
       </c>
       <c r="D9" t="n">
-        <v>-127</v>
+        <v>1091.74</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>786</v>
+        <v>699</v>
       </c>
       <c r="G9" t="n">
-        <v>54.51</v>
+        <v>311.57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2464</v>
+      </c>
+      <c r="L9" t="n">
+        <v>107</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.774</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:37.396</t>
+          <t>2026-05-29 09:38:02.130</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421839447</v>
+        <v>1780022279865</v>
       </c>
       <c r="C10" t="n">
-        <v>86259</v>
+        <v>84668</v>
       </c>
       <c r="D10" t="n">
-        <v>51.35</v>
+        <v>461.15</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>786</v>
+        <v>699</v>
       </c>
       <c r="G10" t="n">
-        <v>54.51</v>
+        <v>311.57</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2264</v>
+      </c>
+      <c r="L10" t="n">
+        <v>109</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.858</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:37.772</t>
+          <t>2026-05-29 09:38:02.156</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421839648</v>
+        <v>1780022280065</v>
       </c>
       <c r="C11" t="n">
-        <v>86322</v>
+        <v>84606</v>
       </c>
       <c r="D11" t="n">
-        <v>111.78</v>
+        <v>376.1</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>805</v>
+        <v>699</v>
       </c>
       <c r="G11" t="n">
-        <v>58.39</v>
+        <v>311.57</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2090</v>
+      </c>
+      <c r="L11" t="n">
+        <v>105</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.787</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:37.772</t>
+          <t>2026-05-29 09:38:02.484</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421839850</v>
+        <v>1780022280265</v>
       </c>
       <c r="C12" t="n">
-        <v>85961</v>
+        <v>85624</v>
       </c>
       <c r="D12" t="n">
-        <v>-254.81</v>
+        <v>1375.29</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F12" t="n">
-        <v>805</v>
+        <v>699</v>
       </c>
       <c r="G12" t="n">
-        <v>58.39</v>
+        <v>311.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2218</v>
+      </c>
+      <c r="L12" t="n">
+        <v>104</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.097</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:38.161</t>
+          <t>2026-05-29 09:38:02.486</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421840051</v>
+        <v>1780022280465</v>
       </c>
       <c r="C13" t="n">
-        <v>86103</v>
+        <v>85747</v>
       </c>
       <c r="D13" t="n">
-        <v>-100.07</v>
+        <v>1429.53</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>805</v>
+        <v>699</v>
       </c>
       <c r="G13" t="n">
-        <v>58.39</v>
+        <v>311.57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L13" t="n">
+        <v>105</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:38.162</t>
+          <t>2026-05-29 09:38:02.487</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421840252</v>
+        <v>1780022280665</v>
       </c>
       <c r="C14" t="n">
-        <v>86353</v>
+        <v>84899</v>
       </c>
       <c r="D14" t="n">
-        <v>154.94</v>
+        <v>510.05</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F14" t="n">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="G14" t="n">
-        <v>61.41</v>
+        <v>311.57</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J14" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L14" t="n">
+        <v>109</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.851</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:38.580</t>
+          <t>2026-05-29 09:38:02.488</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421840454</v>
+        <v>1780022280884</v>
       </c>
       <c r="C15" t="n">
-        <v>85858</v>
+        <v>84840</v>
       </c>
       <c r="D15" t="n">
-        <v>-347.81</v>
+        <v>425.55</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F15" t="n">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="G15" t="n">
-        <v>61.41</v>
+        <v>311.57</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1603</v>
+      </c>
+      <c r="L15" t="n">
+        <v>109</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.824</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:38.580</t>
+          <t>2026-05-29 09:38:03.282</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421840655</v>
+        <v>1780022281084</v>
       </c>
       <c r="C16" t="n">
-        <v>86076</v>
+        <v>84765</v>
       </c>
       <c r="D16" t="n">
-        <v>-112.42</v>
+        <v>329.27</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="G16" t="n">
-        <v>61.41</v>
+        <v>311.57</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J16" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2197</v>
+      </c>
+      <c r="L16" t="n">
+        <v>106</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:38.978</t>
+          <t>2026-05-29 09:38:03.284</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421840857</v>
+        <v>1780022281524</v>
       </c>
       <c r="C17" t="n">
-        <v>86224</v>
+        <v>84205</v>
       </c>
       <c r="D17" t="n">
-        <v>41.2</v>
+        <v>-247.19</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="G17" t="n">
-        <v>61.41</v>
+        <v>311.57</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1759</v>
+      </c>
+      <c r="L17" t="n">
+        <v>108</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.295</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:38.979</t>
+          <t>2026-05-29 09:38:03.285</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421841058</v>
+        <v>1780022281724</v>
       </c>
       <c r="C18" t="n">
-        <v>86422</v>
+        <v>84354</v>
       </c>
       <c r="D18" t="n">
-        <v>237.14</v>
+        <v>-85.83</v>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G18" t="n">
-        <v>62.25</v>
+        <v>311.57</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1560</v>
+      </c>
+      <c r="L18" t="n">
+        <v>110</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.034</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:39.712</t>
+          <t>2026-05-29 09:38:04.589</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421841260</v>
+        <v>1780022281924</v>
       </c>
       <c r="C19" t="n">
-        <v>85885</v>
+        <v>83855</v>
       </c>
       <c r="D19" t="n">
-        <v>-311.72</v>
+        <v>-580.54</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G19" t="n">
-        <v>62.25</v>
+        <v>311.57</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2664</v>
+      </c>
+      <c r="L19" t="n">
+        <v>111</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.549</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:39.722</t>
+          <t>2026-05-29 09:38:04.591</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421841461</v>
+        <v>1780022282124</v>
       </c>
       <c r="C20" t="n">
-        <v>86066</v>
+        <v>85491</v>
       </c>
       <c r="D20" t="n">
-        <v>-115.13</v>
+        <v>1084.49</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F20" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G20" t="n">
-        <v>62.25</v>
+        <v>311.57</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2466</v>
+      </c>
+      <c r="L20" t="n">
+        <v>112</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.409</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:39.723</t>
+          <t>2026-05-29 09:38:04.593</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421841662</v>
+        <v>1780022282324</v>
       </c>
       <c r="C21" t="n">
-        <v>86243</v>
+        <v>85533</v>
       </c>
       <c r="D21" t="n">
-        <v>67.63</v>
+        <v>1072.26</v>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F21" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G21" t="n">
-        <v>62.25</v>
+        <v>311.57</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2268</v>
+      </c>
+      <c r="L21" t="n">
+        <v>105</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:39.723</t>
+          <t>2026-05-29 09:38:04.594</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421841864</v>
+        <v>1780022282524</v>
       </c>
       <c r="C22" t="n">
-        <v>86433</v>
+        <v>85376</v>
       </c>
       <c r="D22" t="n">
-        <v>254.25</v>
+        <v>861.65</v>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F22" t="n">
-        <v>806</v>
+        <v>699</v>
       </c>
       <c r="G22" t="n">
-        <v>60.01</v>
+        <v>311.57</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2069</v>
+      </c>
+      <c r="L22" t="n">
+        <v>106</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.734</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:40.006</t>
+          <t>2026-05-29 09:38:09.484</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421842065</v>
+        <v>1780022282724</v>
       </c>
       <c r="C23" t="n">
-        <v>85824</v>
+        <v>84853</v>
       </c>
       <c r="D23" t="n">
-        <v>-367.47</v>
+        <v>295.57</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F23" t="n">
-        <v>806</v>
+        <v>699</v>
       </c>
       <c r="G23" t="n">
-        <v>60.01</v>
+        <v>311.57</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6759</v>
+      </c>
+      <c r="L23" t="n">
+        <v>105</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:40.007</t>
+          <t>2026-05-29 09:38:09.486</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421842266</v>
+        <v>1780022282924</v>
       </c>
       <c r="C24" t="n">
-        <v>86010</v>
+        <v>84862</v>
       </c>
       <c r="D24" t="n">
-        <v>-163.09</v>
+        <v>289.79</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F24" t="n">
-        <v>806</v>
+        <v>699</v>
       </c>
       <c r="G24" t="n">
-        <v>60.01</v>
+        <v>311.57</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J24" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6560</v>
+      </c>
+      <c r="L24" t="n">
+        <v>113</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:40.407</t>
+          <t>2026-05-29 09:38:09.487</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421842468</v>
+        <v>1780022283124</v>
       </c>
       <c r="C25" t="n">
-        <v>86219</v>
+        <v>84625</v>
       </c>
       <c r="D25" t="n">
-        <v>54.06</v>
+        <v>38.3</v>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F25" t="n">
-        <v>806</v>
+        <v>699</v>
       </c>
       <c r="G25" t="n">
-        <v>60.01</v>
+        <v>311.57</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J25" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6362</v>
+      </c>
+      <c r="L25" t="n">
+        <v>109</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:40.408</t>
+          <t>2026-05-29 09:38:09.489</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421842669</v>
+        <v>1780022286624</v>
       </c>
       <c r="C26" t="n">
-        <v>86376</v>
+        <v>84364</v>
       </c>
       <c r="D26" t="n">
-        <v>208.36</v>
+        <v>-224.62</v>
       </c>
       <c r="E26" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F26" t="n">
-        <v>805</v>
+        <v>699</v>
       </c>
       <c r="G26" t="n">
-        <v>57.21</v>
+        <v>311.57</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2863</v>
+      </c>
+      <c r="L26" t="n">
+        <v>107</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.209</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:40.831</t>
+          <t>2026-05-29 09:38:09.597</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421842871</v>
+        <v>1780022286842</v>
       </c>
       <c r="C27" t="n">
-        <v>85900</v>
+        <v>84984</v>
       </c>
       <c r="D27" t="n">
-        <v>-278.06</v>
+        <v>406.61</v>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F27" t="n">
-        <v>805</v>
+        <v>699</v>
       </c>
       <c r="G27" t="n">
-        <v>57.21</v>
+        <v>311.57</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2754</v>
+      </c>
+      <c r="L27" t="n">
+        <v>109</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.607</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:40.832</t>
+          <t>2026-05-29 09:38:09.598</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421843072</v>
+        <v>1780022287042</v>
       </c>
       <c r="C28" t="n">
-        <v>86080</v>
+        <v>85435</v>
       </c>
       <c r="D28" t="n">
-        <v>-84.16</v>
+        <v>837.28</v>
       </c>
       <c r="E28" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F28" t="n">
-        <v>805</v>
+        <v>699</v>
       </c>
       <c r="G28" t="n">
-        <v>57.21</v>
+        <v>311.57</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2555</v>
+      </c>
+      <c r="L28" t="n">
+        <v>102</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.611</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:41.494</t>
+          <t>2026-05-29 09:38:09.598</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421843273</v>
+        <v>1780022287242</v>
       </c>
       <c r="C29" t="n">
-        <v>86336</v>
+        <v>85412</v>
       </c>
       <c r="D29" t="n">
-        <v>176.05</v>
+        <v>772.42</v>
       </c>
       <c r="E29" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F29" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G29" t="n">
-        <v>59.39</v>
+        <v>311.57</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2356</v>
+      </c>
+      <c r="L29" t="n">
+        <v>111</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:41.514</t>
+          <t>2026-05-29 09:38:09.599</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421843475</v>
+        <v>1780022287442</v>
       </c>
       <c r="C30" t="n">
-        <v>85966</v>
+        <v>85684</v>
       </c>
       <c r="D30" t="n">
-        <v>-202.75</v>
+        <v>1005.8</v>
       </c>
       <c r="E30" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F30" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G30" t="n">
-        <v>59.39</v>
+        <v>311.57</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2157</v>
+      </c>
+      <c r="L30" t="n">
+        <v>105</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.605</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:41.514</t>
+          <t>2026-05-29 09:38:09.601</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421843676</v>
+        <v>1780022287642</v>
       </c>
       <c r="C31" t="n">
-        <v>86080</v>
+        <v>85482</v>
       </c>
       <c r="D31" t="n">
-        <v>-78.61</v>
+        <v>753.51</v>
       </c>
       <c r="E31" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F31" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G31" t="n">
-        <v>59.39</v>
+        <v>311.57</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1958</v>
+      </c>
+      <c r="L31" t="n">
+        <v>106</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.048</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:41.849</t>
+          <t>2026-05-29 09:38:09.611</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421843878</v>
+        <v>1780022287842</v>
       </c>
       <c r="C32" t="n">
-        <v>86244</v>
+        <v>85307</v>
       </c>
       <c r="D32" t="n">
-        <v>89.31999999999999</v>
+        <v>540.83</v>
       </c>
       <c r="E32" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F32" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="G32" t="n">
-        <v>59.39</v>
+        <v>311.57</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1768</v>
+      </c>
+      <c r="L32" t="n">
+        <v>105</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.753</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:41.849</t>
+          <t>2026-05-29 09:38:09.844</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421844079</v>
+        <v>1780022288061</v>
       </c>
       <c r="C33" t="n">
-        <v>86448</v>
+        <v>85058</v>
       </c>
       <c r="D33" t="n">
-        <v>288.85</v>
+        <v>264.79</v>
       </c>
       <c r="E33" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F33" t="n">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="G33" t="n">
-        <v>50.52</v>
+        <v>311.57</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1781</v>
+      </c>
+      <c r="L33" t="n">
+        <v>113</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.312</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:42.261</t>
+          <t>2026-05-29 09:38:09.890</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421844280</v>
+        <v>1780022288261</v>
       </c>
       <c r="C34" t="n">
-        <v>85928</v>
+        <v>84670</v>
       </c>
       <c r="D34" t="n">
-        <v>-245.59</v>
+        <v>-136.45</v>
       </c>
       <c r="E34" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F34" t="n">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="G34" t="n">
-        <v>50.52</v>
+        <v>311.57</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1626</v>
+      </c>
+      <c r="L34" t="n">
+        <v>106</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.778</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:42.263</t>
+          <t>2026-05-29 09:38:09.911</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421844482</v>
+        <v>1780022288461</v>
       </c>
       <c r="C35" t="n">
-        <v>86120</v>
+        <v>84934</v>
       </c>
       <c r="D35" t="n">
-        <v>-41.31</v>
+        <v>134.37</v>
       </c>
       <c r="E35" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F35" t="n">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="G35" t="n">
-        <v>50.52</v>
+        <v>311.57</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1449</v>
+      </c>
+      <c r="L35" t="n">
+        <v>114</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.165</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:42.888</t>
+          <t>2026-05-29 09:38:09.913</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421844683</v>
+        <v>1780022288661</v>
       </c>
       <c r="C36" t="n">
-        <v>86331</v>
+        <v>84943</v>
       </c>
       <c r="D36" t="n">
-        <v>171.75</v>
+        <v>136.66</v>
       </c>
       <c r="E36" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F36" t="n">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="G36" t="n">
-        <v>50.52</v>
+        <v>311.57</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1251</v>
+      </c>
+      <c r="L36" t="n">
+        <v>105</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.057</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:42.889</t>
+          <t>2026-05-29 09:38:10.514</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421844885</v>
+        <v>1780022288861</v>
       </c>
       <c r="C37" t="n">
-        <v>86392</v>
+        <v>84898</v>
       </c>
       <c r="D37" t="n">
-        <v>224.17</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F37" t="n">
-        <v>746</v>
+        <v>699</v>
       </c>
       <c r="G37" t="n">
-        <v>48.71</v>
+        <v>311.57</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1652</v>
+      </c>
+      <c r="L37" t="n">
+        <v>106</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:42.890</t>
+          <t>2026-05-29 09:38:10.661</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421845086</v>
+        <v>1780022289061</v>
       </c>
       <c r="C38" t="n">
-        <v>86015</v>
+        <v>85157</v>
       </c>
       <c r="D38" t="n">
-        <v>-164.04</v>
+        <v>339.58</v>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F38" t="n">
-        <v>746</v>
+        <v>699</v>
       </c>
       <c r="G38" t="n">
-        <v>48.71</v>
+        <v>311.57</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J38" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1598</v>
+      </c>
+      <c r="L38" t="n">
+        <v>111</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.123</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:43.477</t>
+          <t>2026-05-29 09:38:10.662</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421845288</v>
+        <v>1780022289301</v>
       </c>
       <c r="C39" t="n">
-        <v>86202</v>
+        <v>86222</v>
       </c>
       <c r="D39" t="n">
-        <v>31.16</v>
+        <v>1387.6</v>
       </c>
       <c r="E39" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F39" t="n">
-        <v>746</v>
+        <v>10216</v>
       </c>
       <c r="G39" t="n">
-        <v>48.71</v>
+        <v>311.57</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>65.23</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1360</v>
+      </c>
+      <c r="L39" t="n">
+        <v>117</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.172</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:43.479</t>
+          <t>2026-05-29 09:38:10.664</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421845489</v>
+        <v>1780022289501</v>
       </c>
       <c r="C40" t="n">
-        <v>86392</v>
+        <v>89295</v>
       </c>
       <c r="D40" t="n">
-        <v>219.6</v>
+        <v>4391.22</v>
       </c>
       <c r="E40" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F40" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G40" t="n">
-        <v>47.16</v>
+        <v>311.57</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L40" t="n">
+        <v>115</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.031</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:43.521</t>
+          <t>2026-05-29 09:38:10.665</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421845690</v>
+        <v>1780022289701</v>
       </c>
       <c r="C41" t="n">
-        <v>85945</v>
+        <v>85630</v>
       </c>
       <c r="D41" t="n">
-        <v>-238.38</v>
+        <v>506.66</v>
       </c>
       <c r="E41" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F41" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G41" t="n">
-        <v>47.16</v>
+        <v>311.57</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K41" t="n">
+        <v>963</v>
+      </c>
+      <c r="L41" t="n">
+        <v>114</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.167</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:43.942</t>
+          <t>2026-05-29 09:38:11.411</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421845892</v>
+        <v>1780022289901</v>
       </c>
       <c r="C42" t="n">
-        <v>86176</v>
+        <v>85490</v>
       </c>
       <c r="D42" t="n">
-        <v>4.54</v>
+        <v>341.33</v>
       </c>
       <c r="E42" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F42" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G42" t="n">
-        <v>47.16</v>
+        <v>311.57</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1510</v>
+      </c>
+      <c r="L42" t="n">
+        <v>111</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.585</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:43.943</t>
+          <t>2026-05-29 09:38:11.412</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421846093</v>
+        <v>1780022290101</v>
       </c>
       <c r="C43" t="n">
-        <v>86421</v>
+        <v>86367</v>
       </c>
       <c r="D43" t="n">
-        <v>249.31</v>
+        <v>1201.26</v>
       </c>
       <c r="E43" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F43" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G43" t="n">
-        <v>47.16</v>
+        <v>311.57</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1311</v>
+      </c>
+      <c r="L43" t="n">
+        <v>121</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.577</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:44.315</t>
+          <t>2026-05-29 09:38:12.004</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421846295</v>
+        <v>1780022290320</v>
       </c>
       <c r="C44" t="n">
-        <v>86465</v>
+        <v>86291</v>
       </c>
       <c r="D44" t="n">
-        <v>280.85</v>
+        <v>1065.2</v>
       </c>
       <c r="E44" t="n">
         <v>83</v>
       </c>
       <c r="F44" t="n">
-        <v>664</v>
+        <v>10216</v>
       </c>
       <c r="G44" t="n">
-        <v>52.13</v>
+        <v>311.57</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1683</v>
+      </c>
+      <c r="L44" t="n">
+        <v>120</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.105</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:44.317</t>
+          <t>2026-05-29 09:38:12.005</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421846496</v>
+        <v>1780022290520</v>
       </c>
       <c r="C45" t="n">
-        <v>86122</v>
+        <v>86877</v>
       </c>
       <c r="D45" t="n">
-        <v>-76.19</v>
+        <v>1597.94</v>
       </c>
       <c r="E45" t="n">
         <v>83</v>
       </c>
       <c r="F45" t="n">
-        <v>664</v>
+        <v>10216</v>
       </c>
       <c r="G45" t="n">
-        <v>52.13</v>
+        <v>311.57</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1484</v>
+      </c>
+      <c r="L45" t="n">
+        <v>127</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.792</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:45.137</t>
+          <t>2026-05-29 09:38:12.006</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421846697</v>
+        <v>1780022290720</v>
       </c>
       <c r="C46" t="n">
-        <v>86315</v>
+        <v>86099</v>
       </c>
       <c r="D46" t="n">
-        <v>120.62</v>
+        <v>740.04</v>
       </c>
       <c r="E46" t="n">
         <v>83</v>
       </c>
       <c r="F46" t="n">
-        <v>664</v>
+        <v>10216</v>
       </c>
       <c r="G46" t="n">
-        <v>52.13</v>
+        <v>311.57</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1285</v>
+      </c>
+      <c r="L46" t="n">
+        <v>114</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.886</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:45.138</t>
+          <t>2026-05-29 09:38:12.007</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421846899</v>
+        <v>1780022290920</v>
       </c>
       <c r="C47" t="n">
-        <v>86552</v>
+        <v>86046</v>
       </c>
       <c r="D47" t="n">
-        <v>351.58</v>
+        <v>650.04</v>
       </c>
       <c r="E47" t="n">
         <v>83</v>
       </c>
       <c r="F47" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G47" t="n">
-        <v>46.37</v>
+        <v>311.57</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1086</v>
+      </c>
+      <c r="L47" t="n">
+        <v>112</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.019</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:45.139</t>
+          <t>2026-05-29 09:38:12.515</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421847100</v>
+        <v>1780022291121</v>
       </c>
       <c r="C48" t="n">
-        <v>86046</v>
+        <v>86429</v>
       </c>
       <c r="D48" t="n">
-        <v>-171.99</v>
+        <v>1000.54</v>
       </c>
       <c r="E48" t="n">
         <v>83</v>
       </c>
       <c r="F48" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G48" t="n">
-        <v>46.37</v>
+        <v>311.57</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1393</v>
+      </c>
+      <c r="L48" t="n">
+        <v>112</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.168</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:45.140</t>
+          <t>2026-05-29 09:38:12.517</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421847302</v>
+        <v>1780022291320</v>
       </c>
       <c r="C49" t="n">
-        <v>86223</v>
+        <v>86817</v>
       </c>
       <c r="D49" t="n">
-        <v>13.6</v>
+        <v>1338.51</v>
       </c>
       <c r="E49" t="n">
         <v>83</v>
       </c>
       <c r="F49" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G49" t="n">
-        <v>46.37</v>
+        <v>311.57</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1196</v>
+      </c>
+      <c r="L49" t="n">
+        <v>123</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:45.555</t>
+          <t>2026-05-29 09:38:12.519</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421847503</v>
+        <v>1780022291521</v>
       </c>
       <c r="C50" t="n">
-        <v>86407</v>
+        <v>86903</v>
       </c>
       <c r="D50" t="n">
-        <v>196.92</v>
+        <v>1357.59</v>
       </c>
       <c r="E50" t="n">
         <v>83</v>
       </c>
       <c r="F50" t="n">
-        <v>725</v>
+        <v>10216</v>
       </c>
       <c r="G50" t="n">
-        <v>46.37</v>
+        <v>311.57</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K50" t="n">
+        <v>997</v>
+      </c>
+      <c r="L50" t="n">
+        <v>110</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:45.556</t>
+          <t>2026-05-29 09:38:12.857</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421847705</v>
+        <v>1780022291720</v>
       </c>
       <c r="C51" t="n">
-        <v>86610</v>
+        <v>87193</v>
       </c>
       <c r="D51" t="n">
-        <v>390.08</v>
+        <v>1579.71</v>
       </c>
       <c r="E51" t="n">
         <v>83</v>
       </c>
       <c r="F51" t="n">
-        <v>746</v>
+        <v>10216</v>
       </c>
       <c r="G51" t="n">
-        <v>43.87</v>
+        <v>311.57</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L51" t="n">
+        <v>123</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.067</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:46.147</t>
+          <t>2026-05-29 09:38:12.885</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421847906</v>
+        <v>1780022291920</v>
       </c>
       <c r="C52" t="n">
-        <v>86080</v>
+        <v>87915</v>
       </c>
       <c r="D52" t="n">
-        <v>-159.43</v>
+        <v>2222.72</v>
       </c>
       <c r="E52" t="n">
         <v>83</v>
       </c>
       <c r="F52" t="n">
-        <v>746</v>
+        <v>10216</v>
       </c>
       <c r="G52" t="n">
-        <v>43.87</v>
+        <v>311.57</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>965</v>
+      </c>
+      <c r="L52" t="n">
+        <v>102</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:46.148</t>
+          <t>2026-05-29 09:38:12.893</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421848107</v>
+        <v>1780022292120</v>
       </c>
       <c r="C53" t="n">
-        <v>86262</v>
+        <v>87113</v>
       </c>
       <c r="D53" t="n">
-        <v>30.55</v>
+        <v>1309.58</v>
       </c>
       <c r="E53" t="n">
         <v>83</v>
       </c>
       <c r="F53" t="n">
-        <v>746</v>
+        <v>10216</v>
       </c>
       <c r="G53" t="n">
-        <v>43.87</v>
+        <v>311.57</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>772</v>
+      </c>
+      <c r="L53" t="n">
+        <v>112</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.492</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:46.148</t>
+          <t>2026-05-29 09:38:14.875</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421848309</v>
+        <v>1780022292320</v>
       </c>
       <c r="C54" t="n">
-        <v>86407</v>
+        <v>86406</v>
       </c>
       <c r="D54" t="n">
-        <v>174.02</v>
+        <v>537.11</v>
       </c>
       <c r="E54" t="n">
         <v>83</v>
       </c>
       <c r="F54" t="n">
-        <v>746</v>
+        <v>10216</v>
       </c>
       <c r="G54" t="n">
-        <v>43.87</v>
+        <v>311.57</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2553</v>
+      </c>
+      <c r="L54" t="n">
+        <v>121</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.459</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.607</t>
+          <t>2026-05-29 09:38:14.876</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421848510</v>
+        <v>1780022292539</v>
       </c>
       <c r="C55" t="n">
-        <v>86433</v>
+        <v>86258</v>
       </c>
       <c r="D55" t="n">
-        <v>191.32</v>
+        <v>362.25</v>
       </c>
       <c r="E55" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F55" t="n">
-        <v>805</v>
+        <v>10216</v>
       </c>
       <c r="G55" t="n">
-        <v>47.47</v>
+        <v>311.57</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2336</v>
+      </c>
+      <c r="L55" t="n">
+        <v>111</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.753</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.607</t>
+          <t>2026-05-29 09:38:14.877</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421848712</v>
+        <v>1780022292739</v>
       </c>
       <c r="C56" t="n">
-        <v>86094</v>
+        <v>85806</v>
       </c>
       <c r="D56" t="n">
-        <v>-157.25</v>
+        <v>-107.86</v>
       </c>
       <c r="E56" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F56" t="n">
-        <v>805</v>
+        <v>10216</v>
       </c>
       <c r="G56" t="n">
-        <v>47.47</v>
+        <v>311.57</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2137</v>
+      </c>
+      <c r="L56" t="n">
+        <v>125</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.541</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.632</t>
+          <t>2026-05-29 09:38:15.684</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421848913</v>
+        <v>1780022292939</v>
       </c>
       <c r="C57" t="n">
-        <v>86269</v>
+        <v>86749</v>
       </c>
       <c r="D57" t="n">
-        <v>25.61</v>
+        <v>840.53</v>
       </c>
       <c r="E57" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F57" t="n">
-        <v>805</v>
+        <v>10216</v>
       </c>
       <c r="G57" t="n">
-        <v>47.47</v>
+        <v>311.57</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2744</v>
+      </c>
+      <c r="L57" t="n">
+        <v>109</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.631</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.633</t>
+          <t>2026-05-29 09:38:15.686</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421849114</v>
+        <v>1780022293139</v>
       </c>
       <c r="C58" t="n">
-        <v>86499</v>
+        <v>87025</v>
       </c>
       <c r="D58" t="n">
-        <v>254.33</v>
+        <v>1074.5</v>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F58" t="n">
-        <v>685</v>
+        <v>10216</v>
       </c>
       <c r="G58" t="n">
-        <v>45.64</v>
+        <v>311.57</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2546</v>
+      </c>
+      <c r="L58" t="n">
+        <v>112</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.475</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.633</t>
+          <t>2026-05-29 09:38:15.688</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421849316</v>
+        <v>1780022293339</v>
       </c>
       <c r="C59" t="n">
-        <v>85993</v>
+        <v>86859</v>
       </c>
       <c r="D59" t="n">
-        <v>-264.38</v>
+        <v>854.78</v>
       </c>
       <c r="E59" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F59" t="n">
-        <v>685</v>
+        <v>10216</v>
       </c>
       <c r="G59" t="n">
-        <v>45.64</v>
+        <v>311.57</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2347</v>
+      </c>
+      <c r="L59" t="n">
+        <v>116</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.704</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.634</t>
+          <t>2026-05-29 09:38:15.689</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421849517</v>
+        <v>1780022293539</v>
       </c>
       <c r="C60" t="n">
-        <v>86209</v>
+        <v>86985</v>
       </c>
       <c r="D60" t="n">
-        <v>-35.16</v>
+        <v>938.04</v>
       </c>
       <c r="E60" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F60" t="n">
-        <v>685</v>
+        <v>10216</v>
       </c>
       <c r="G60" t="n">
-        <v>45.64</v>
+        <v>311.57</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2149</v>
+      </c>
+      <c r="L60" t="n">
+        <v>125</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.132</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.792</t>
+          <t>2026-05-29 09:38:17.311</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421849719</v>
+        <v>1780022293739</v>
       </c>
       <c r="C61" t="n">
-        <v>86403</v>
+        <v>86931</v>
       </c>
       <c r="D61" t="n">
-        <v>160.59</v>
+        <v>837.14</v>
       </c>
       <c r="E61" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F61" t="n">
-        <v>685</v>
+        <v>10216</v>
       </c>
       <c r="G61" t="n">
-        <v>45.64</v>
+        <v>311.57</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J61" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3570</v>
+      </c>
+      <c r="L61" t="n">
+        <v>122</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.348</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:47.970</t>
+          <t>2026-05-29 09:38:17.313</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421849920</v>
+        <v>1780022293939</v>
       </c>
       <c r="C62" t="n">
-        <v>86464</v>
+        <v>86492</v>
       </c>
       <c r="D62" t="n">
-        <v>213.56</v>
+        <v>356.28</v>
       </c>
       <c r="E62" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F62" t="n">
-        <v>685</v>
+        <v>10216</v>
       </c>
       <c r="G62" t="n">
-        <v>40.07</v>
+        <v>311.57</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J62" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3373</v>
+      </c>
+      <c r="L62" t="n">
+        <v>112</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.435</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:48.412</t>
+          <t>2026-05-29 09:38:17.314</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421850122</v>
+        <v>1780022294139</v>
       </c>
       <c r="C63" t="n">
-        <v>85997</v>
+        <v>85628</v>
       </c>
       <c r="D63" t="n">
-        <v>-264.11</v>
+        <v>-525.53</v>
       </c>
       <c r="E63" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F63" t="n">
-        <v>685</v>
+        <v>10216</v>
       </c>
       <c r="G63" t="n">
-        <v>40.07</v>
+        <v>311.57</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J63" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3174</v>
+      </c>
+      <c r="L63" t="n">
+        <v>124</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.651</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:48.424</t>
+          <t>2026-05-29 09:38:17.315</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421850323</v>
+        <v>1780022294339</v>
       </c>
       <c r="C64" t="n">
-        <v>86209</v>
+        <v>85222</v>
       </c>
       <c r="D64" t="n">
-        <v>-38.91</v>
+        <v>-905.26</v>
       </c>
       <c r="E64" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F64" t="n">
-        <v>685</v>
+        <v>10216</v>
       </c>
       <c r="G64" t="n">
-        <v>40.07</v>
+        <v>311.57</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2975</v>
+      </c>
+      <c r="L64" t="n">
+        <v>113</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.623</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:48.439</t>
+          <t>2026-05-29 09:38:17.315</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421850524</v>
+        <v>1780022294539</v>
       </c>
       <c r="C65" t="n">
-        <v>86474</v>
+        <v>85329</v>
       </c>
       <c r="D65" t="n">
-        <v>228.04</v>
+        <v>-752.99</v>
       </c>
       <c r="E65" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F65" t="n">
-        <v>745</v>
+        <v>10216</v>
       </c>
       <c r="G65" t="n">
-        <v>40.28</v>
+        <v>311.57</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2776</v>
+      </c>
+      <c r="L65" t="n">
+        <v>120</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.644</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:48.897</t>
+          <t>2026-05-29 09:38:17.316</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421850726</v>
+        <v>1780022294758</v>
       </c>
       <c r="C66" t="n">
-        <v>85970</v>
+        <v>85846</v>
       </c>
       <c r="D66" t="n">
-        <v>-287.36</v>
+        <v>-198.34</v>
       </c>
       <c r="E66" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F66" t="n">
-        <v>745</v>
+        <v>10216</v>
       </c>
       <c r="G66" t="n">
-        <v>40.28</v>
+        <v>311.57</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2558</v>
+      </c>
+      <c r="L66" t="n">
+        <v>117</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.576</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:48.898</t>
+          <t>2026-05-29 09:38:17.317</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421850927</v>
+        <v>1780022294958</v>
       </c>
       <c r="C67" t="n">
-        <v>86087</v>
+        <v>85623</v>
       </c>
       <c r="D67" t="n">
-        <v>-156</v>
+        <v>-411.43</v>
       </c>
       <c r="E67" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F67" t="n">
-        <v>745</v>
+        <v>10216</v>
       </c>
       <c r="G67" t="n">
-        <v>40.28</v>
+        <v>311.57</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2358</v>
+      </c>
+      <c r="L67" t="n">
+        <v>114</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.579</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:49.231</t>
+          <t>2026-05-29 09:38:17.317</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421851129</v>
+        <v>1780022295158</v>
       </c>
       <c r="C68" t="n">
-        <v>86250</v>
+        <v>85910</v>
       </c>
       <c r="D68" t="n">
-        <v>14.8</v>
+        <v>-103.86</v>
       </c>
       <c r="E68" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F68" t="n">
-        <v>745</v>
+        <v>10216</v>
       </c>
       <c r="G68" t="n">
-        <v>40.28</v>
+        <v>311.57</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2159</v>
+      </c>
+      <c r="L68" t="n">
+        <v>112</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.646</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:49.231</t>
+          <t>2026-05-29 09:38:17.318</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421851330</v>
+        <v>1780022295358</v>
       </c>
       <c r="C69" t="n">
-        <v>86423</v>
+        <v>86244</v>
       </c>
       <c r="D69" t="n">
-        <v>187.06</v>
+        <v>235.34</v>
       </c>
       <c r="E69" t="n">
         <v>83</v>
       </c>
       <c r="F69" t="n">
-        <v>766</v>
+        <v>5937</v>
       </c>
       <c r="G69" t="n">
-        <v>42.31</v>
+        <v>311.57</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L69" t="n">
+        <v>118</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.545</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:49.632</t>
+          <t>2026-05-29 09:38:17.319</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421851531</v>
+        <v>1780022295558</v>
       </c>
       <c r="C70" t="n">
-        <v>85856</v>
+        <v>85864</v>
       </c>
       <c r="D70" t="n">
-        <v>-389.29</v>
+        <v>-156.43</v>
       </c>
       <c r="E70" t="n">
         <v>83</v>
       </c>
       <c r="F70" t="n">
-        <v>766</v>
+        <v>5937</v>
       </c>
       <c r="G70" t="n">
-        <v>42.31</v>
+        <v>311.57</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1760</v>
+      </c>
+      <c r="L70" t="n">
+        <v>111</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.534</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:49.638</t>
+          <t>2026-05-29 09:38:17.319</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421851733</v>
+        <v>1780022295758</v>
       </c>
       <c r="C71" t="n">
-        <v>86043</v>
+        <v>85508</v>
       </c>
       <c r="D71" t="n">
-        <v>-182.83</v>
+        <v>-504.61</v>
       </c>
       <c r="E71" t="n">
         <v>83</v>
       </c>
       <c r="F71" t="n">
-        <v>766</v>
+        <v>5937</v>
       </c>
       <c r="G71" t="n">
-        <v>42.31</v>
+        <v>311.57</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1561</v>
+      </c>
+      <c r="L71" t="n">
+        <v>112</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.524</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:49.830</t>
+          <t>2026-05-29 09:38:17.643</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421851934</v>
+        <v>1780022295958</v>
       </c>
       <c r="C72" t="n">
-        <v>86218</v>
+        <v>85473</v>
       </c>
       <c r="D72" t="n">
-        <v>1.32</v>
+        <v>-514.38</v>
       </c>
       <c r="E72" t="n">
         <v>83</v>
       </c>
       <c r="F72" t="n">
-        <v>766</v>
+        <v>5937</v>
       </c>
       <c r="G72" t="n">
-        <v>42.31</v>
+        <v>311.57</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1684</v>
+      </c>
+      <c r="L72" t="n">
+        <v>113</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.002</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:50.349</t>
+          <t>2026-05-29 09:38:17.669</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421852136</v>
+        <v>1780022296158</v>
       </c>
       <c r="C73" t="n">
-        <v>86169</v>
+        <v>87462</v>
       </c>
       <c r="D73" t="n">
-        <v>-47.75</v>
+        <v>1500.34</v>
       </c>
       <c r="E73" t="n">
         <v>81</v>
       </c>
       <c r="F73" t="n">
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="G73" t="n">
-        <v>42.26</v>
+        <v>296.97</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1509</v>
+      </c>
+      <c r="L73" t="n">
+        <v>116</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.909</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:50.349</t>
+          <t>2026-05-29 09:38:17.683</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421852337</v>
+        <v>1780022296358</v>
       </c>
       <c r="C74" t="n">
-        <v>85944</v>
+        <v>85981</v>
       </c>
       <c r="D74" t="n">
-        <v>-270.36</v>
+        <v>-55.68</v>
       </c>
       <c r="E74" t="n">
         <v>81</v>
       </c>
       <c r="F74" t="n">
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="G74" t="n">
-        <v>42.26</v>
+        <v>296.97</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1324</v>
+      </c>
+      <c r="L74" t="n">
+        <v>109</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.299</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:50.350</t>
+          <t>2026-05-29 09:38:17.698</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421852538</v>
+        <v>1780022296577</v>
       </c>
       <c r="C75" t="n">
-        <v>86148</v>
+        <v>85011</v>
       </c>
       <c r="D75" t="n">
-        <v>-52.84</v>
+        <v>-1022.89</v>
       </c>
       <c r="E75" t="n">
         <v>81</v>
       </c>
       <c r="F75" t="n">
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="G75" t="n">
-        <v>42.26</v>
+        <v>296.97</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L75" t="n">
+        <v>107</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.632</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:50.668</t>
+          <t>2026-05-29 09:38:17.767</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421852740</v>
+        <v>1780022296777</v>
       </c>
       <c r="C76" t="n">
-        <v>86361</v>
+        <v>84762</v>
       </c>
       <c r="D76" t="n">
-        <v>162.8</v>
+        <v>-1220.75</v>
       </c>
       <c r="E76" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F76" t="n">
-        <v>664</v>
+        <v>900</v>
       </c>
       <c r="G76" t="n">
-        <v>47.05</v>
+        <v>296.97</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K76" t="n">
+        <v>990</v>
+      </c>
+      <c r="L76" t="n">
+        <v>105</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.733</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:51.056</t>
+          <t>2026-05-29 09:38:18.062</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421852941</v>
+        <v>1780022296977</v>
       </c>
       <c r="C77" t="n">
-        <v>85800</v>
+        <v>84913</v>
       </c>
       <c r="D77" t="n">
-        <v>-406.34</v>
+        <v>-1008.71</v>
       </c>
       <c r="E77" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F77" t="n">
-        <v>664</v>
+        <v>900</v>
       </c>
       <c r="G77" t="n">
-        <v>47.05</v>
+        <v>296.97</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L77" t="n">
+        <v>104</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.749</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:51.057</t>
+          <t>2026-05-29 09:38:18.244</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421853143</v>
+        <v>1780022297177</v>
       </c>
       <c r="C78" t="n">
-        <v>85988</v>
+        <v>86025</v>
       </c>
       <c r="D78" t="n">
-        <v>-198.02</v>
+        <v>153.73</v>
       </c>
       <c r="E78" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F78" t="n">
-        <v>664</v>
+        <v>900</v>
       </c>
       <c r="G78" t="n">
-        <v>47.05</v>
+        <v>296.97</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L78" t="n">
+        <v>106</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.081</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:51.057</t>
+          <t>2026-05-29 09:38:18.252</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421853344</v>
+        <v>1780022297377</v>
       </c>
       <c r="C79" t="n">
-        <v>86170</v>
+        <v>87497</v>
       </c>
       <c r="D79" t="n">
-        <v>-6.12</v>
+        <v>1618.04</v>
       </c>
       <c r="E79" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F79" t="n">
-        <v>664</v>
+        <v>900</v>
       </c>
       <c r="G79" t="n">
-        <v>47.05</v>
+        <v>296.97</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>874</v>
+      </c>
+      <c r="L79" t="n">
+        <v>106</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.086</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:51.465</t>
+          <t>2026-05-29 09:38:18.585</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421853545</v>
+        <v>1780022297577</v>
       </c>
       <c r="C80" t="n">
-        <v>86373</v>
+        <v>86477</v>
       </c>
       <c r="D80" t="n">
-        <v>197.18</v>
+        <v>517.14</v>
       </c>
       <c r="E80" t="n">
         <v>81</v>
       </c>
       <c r="F80" t="n">
-        <v>766</v>
+        <v>900</v>
       </c>
       <c r="G80" t="n">
-        <v>43.78</v>
+        <v>296.97</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L80" t="n">
+        <v>110</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:51.465</t>
+          <t>2026-05-29 09:38:18.587</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421853747</v>
+        <v>1780022297777</v>
       </c>
       <c r="C81" t="n">
-        <v>85753</v>
+        <v>86018</v>
       </c>
       <c r="D81" t="n">
-        <v>-432.68</v>
+        <v>32.28</v>
       </c>
       <c r="E81" t="n">
         <v>81</v>
       </c>
       <c r="F81" t="n">
-        <v>766</v>
+        <v>900</v>
       </c>
       <c r="G81" t="n">
-        <v>43.78</v>
+        <v>296.97</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>809</v>
+      </c>
+      <c r="L81" t="n">
+        <v>103</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.898</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:52.095</t>
+          <t>2026-05-29 09:38:19.799</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421853948</v>
+        <v>1780022297977</v>
       </c>
       <c r="C82" t="n">
-        <v>85950</v>
+        <v>86535</v>
       </c>
       <c r="D82" t="n">
-        <v>-214.04</v>
+        <v>547.67</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
       </c>
       <c r="F82" t="n">
-        <v>766</v>
+        <v>900</v>
       </c>
       <c r="G82" t="n">
-        <v>43.78</v>
+        <v>296.97</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1821</v>
+      </c>
+      <c r="L82" t="n">
+        <v>112</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.746</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:52.099</t>
+          <t>2026-05-29 09:38:19.816</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421854150</v>
+        <v>1780022298177</v>
       </c>
       <c r="C83" t="n">
-        <v>86137</v>
+        <v>86687</v>
       </c>
       <c r="D83" t="n">
-        <v>-16.34</v>
+        <v>672.28</v>
       </c>
       <c r="E83" t="n">
         <v>81</v>
       </c>
       <c r="F83" t="n">
-        <v>766</v>
+        <v>900</v>
       </c>
       <c r="G83" t="n">
-        <v>43.78</v>
+        <v>296.97</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1638</v>
+      </c>
+      <c r="L83" t="n">
+        <v>106</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.313</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:52.100</t>
+          <t>2026-05-29 09:38:19.943</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421854351</v>
+        <v>1780022298377</v>
       </c>
       <c r="C84" t="n">
-        <v>85904</v>
+        <v>85784</v>
       </c>
       <c r="D84" t="n">
-        <v>-248.52</v>
+        <v>-264.33</v>
       </c>
       <c r="E84" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F84" t="n">
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="G84" t="n">
-        <v>43.82</v>
+        <v>296.97</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1564</v>
+      </c>
+      <c r="L84" t="n">
+        <v>108</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.176</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:52.496</t>
+          <t>2026-05-29 09:38:20.049</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421854552</v>
+        <v>1780022298596</v>
       </c>
       <c r="C85" t="n">
-        <v>85864</v>
+        <v>85206</v>
       </c>
       <c r="D85" t="n">
-        <v>-276.1</v>
+        <v>-829.11</v>
       </c>
       <c r="E85" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F85" t="n">
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="G85" t="n">
-        <v>43.82</v>
+        <v>296.97</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1452</v>
+      </c>
+      <c r="L85" t="n">
+        <v>105</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.788</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:52.500</t>
+          <t>2026-05-29 09:38:20.080</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421854754</v>
+        <v>1780022298796</v>
       </c>
       <c r="C86" t="n">
-        <v>85999</v>
+        <v>84949</v>
       </c>
       <c r="D86" t="n">
-        <v>-127.29</v>
+        <v>-1044.66</v>
       </c>
       <c r="E86" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F86" t="n">
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="G86" t="n">
-        <v>43.82</v>
+        <v>296.97</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1282</v>
+      </c>
+      <c r="L86" t="n">
+        <v>106</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.533</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:52.912</t>
+          <t>2026-05-29 09:38:20.081</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421854955</v>
+        <v>1780022298996</v>
       </c>
       <c r="C87" t="n">
-        <v>86202</v>
+        <v>85524</v>
       </c>
       <c r="D87" t="n">
-        <v>82.06999999999999</v>
+        <v>-417.43</v>
       </c>
       <c r="E87" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F87" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="G87" t="n">
-        <v>44.61</v>
+        <v>296.97</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1084</v>
+      </c>
+      <c r="L87" t="n">
+        <v>103</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.858</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:52.947</t>
+          <t>2026-05-29 09:38:20.607</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421855157</v>
+        <v>1780022299196</v>
       </c>
       <c r="C88" t="n">
-        <v>85714</v>
+        <v>85570</v>
       </c>
       <c r="D88" t="n">
-        <v>-410.03</v>
+        <v>-350.55</v>
       </c>
       <c r="E88" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F88" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="G88" t="n">
-        <v>44.61</v>
+        <v>296.97</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1410</v>
+      </c>
+      <c r="L88" t="n">
+        <v>104</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.715</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:53.313</t>
+          <t>2026-05-29 09:38:20.614</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421855358</v>
+        <v>1780022299396</v>
       </c>
       <c r="C89" t="n">
-        <v>85939</v>
+        <v>84698</v>
       </c>
       <c r="D89" t="n">
-        <v>-164.53</v>
+        <v>-1205.03</v>
       </c>
       <c r="E89" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F89" t="n">
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="G89" t="n">
-        <v>44.61</v>
+        <v>296.97</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1217</v>
+      </c>
+      <c r="L89" t="n">
+        <v>113</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.973</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:53.313</t>
+          <t>2026-05-29 09:38:21.345</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421855560</v>
+        <v>1780022299596</v>
       </c>
       <c r="C90" t="n">
-        <v>86172</v>
+        <v>85018</v>
       </c>
       <c r="D90" t="n">
-        <v>76.7</v>
+        <v>-824.78</v>
       </c>
       <c r="E90" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F90" t="n">
-        <v>665</v>
+        <v>900</v>
       </c>
       <c r="G90" t="n">
-        <v>40.63</v>
+        <v>296.97</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1747</v>
+      </c>
+      <c r="L90" t="n">
+        <v>116</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.498</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:53.846</t>
+          <t>2026-05-29 09:38:21.346</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421855761</v>
+        <v>1780022299796</v>
       </c>
       <c r="C91" t="n">
-        <v>86072</v>
+        <v>85323</v>
       </c>
       <c r="D91" t="n">
-        <v>-27.14</v>
+        <v>-478.54</v>
       </c>
       <c r="E91" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F91" t="n">
-        <v>665</v>
+        <v>900</v>
       </c>
       <c r="G91" t="n">
-        <v>40.63</v>
+        <v>296.97</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1549</v>
+      </c>
+      <c r="L91" t="n">
+        <v>111</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.018</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:53.848</t>
+          <t>2026-05-29 09:38:21.348</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421855962</v>
+        <v>1780022299996</v>
       </c>
       <c r="C92" t="n">
-        <v>85781</v>
+        <v>84413</v>
       </c>
       <c r="D92" t="n">
-        <v>-316.78</v>
+        <v>-1364.61</v>
       </c>
       <c r="E92" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F92" t="n">
-        <v>665</v>
+        <v>900</v>
       </c>
       <c r="G92" t="n">
-        <v>40.63</v>
+        <v>296.97</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1351</v>
+      </c>
+      <c r="L92" t="n">
+        <v>104</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.081</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:54.148</t>
+          <t>2026-05-29 09:38:24.622</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421856164</v>
+        <v>1780022300196</v>
       </c>
       <c r="C93" t="n">
-        <v>85976</v>
+        <v>83509</v>
       </c>
       <c r="D93" t="n">
-        <v>-105.94</v>
+        <v>-2200.38</v>
       </c>
       <c r="E93" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F93" t="n">
-        <v>665</v>
+        <v>900</v>
       </c>
       <c r="G93" t="n">
-        <v>40.63</v>
+        <v>296.97</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4425</v>
+      </c>
+      <c r="L93" t="n">
+        <v>116</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:54.179</t>
+          <t>2026-05-29 09:38:24.636</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421856365</v>
+        <v>1780022300396</v>
       </c>
       <c r="C94" t="n">
-        <v>86172</v>
+        <v>82647</v>
       </c>
       <c r="D94" t="n">
-        <v>95.34999999999999</v>
+        <v>-2952.36</v>
       </c>
       <c r="E94" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F94" t="n">
-        <v>765</v>
+        <v>900</v>
       </c>
       <c r="G94" t="n">
-        <v>41.48</v>
+        <v>296.97</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4240</v>
+      </c>
+      <c r="L94" t="n">
+        <v>117</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.536</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:54.564</t>
+          <t>2026-05-29 09:38:24.641</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421856567</v>
+        <v>1780022300615</v>
       </c>
       <c r="C95" t="n">
-        <v>85730</v>
+        <v>83294</v>
       </c>
       <c r="D95" t="n">
-        <v>-351.41</v>
+        <v>-2157.74</v>
       </c>
       <c r="E95" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F95" t="n">
-        <v>765</v>
+        <v>900</v>
       </c>
       <c r="G95" t="n">
-        <v>41.48</v>
+        <v>296.97</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L95" t="n">
+        <v>107</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.756</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:54.622</t>
+          <t>2026-05-29 09:38:24.643</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421856768</v>
+        <v>1780022300815</v>
       </c>
       <c r="C96" t="n">
-        <v>85878</v>
+        <v>84061</v>
       </c>
       <c r="D96" t="n">
-        <v>-185.84</v>
+        <v>-1282.86</v>
       </c>
       <c r="E96" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F96" t="n">
-        <v>765</v>
+        <v>900</v>
       </c>
       <c r="G96" t="n">
-        <v>41.48</v>
+        <v>296.97</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3827</v>
+      </c>
+      <c r="L96" t="n">
+        <v>106</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:50:54.948</t>
+          <t>2026-05-29 09:38:33.886</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421856969</v>
+        <v>1780022301015</v>
       </c>
       <c r="C97" t="n">
-        <v>86037</v>
+        <v>83313</v>
       </c>
       <c r="D97" t="n">
-        <v>-17.55</v>
+        <v>-1966.71</v>
       </c>
       <c r="E97" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F97" t="n">
-        <v>765</v>
+        <v>900</v>
       </c>
       <c r="G97" t="n">
-        <v>41.48</v>
+        <v>296.97</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:54.949</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>1779421857171</v>
-      </c>
-      <c r="C98" t="n">
-        <v>86220</v>
-      </c>
-      <c r="D98" t="n">
-        <v>166.33</v>
-      </c>
-      <c r="E98" t="n">
-        <v>83</v>
-      </c>
-      <c r="F98" t="n">
-        <v>745</v>
-      </c>
-      <c r="G98" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:55.361</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>1779421857372</v>
-      </c>
-      <c r="C99" t="n">
-        <v>85685</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-376.99</v>
-      </c>
-      <c r="E99" t="n">
-        <v>83</v>
-      </c>
-      <c r="F99" t="n">
-        <v>745</v>
-      </c>
-      <c r="G99" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:55.361</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>1779421857574</v>
-      </c>
-      <c r="C100" t="n">
-        <v>85883</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-160.14</v>
-      </c>
-      <c r="E100" t="n">
-        <v>83</v>
-      </c>
-      <c r="F100" t="n">
-        <v>745</v>
-      </c>
-      <c r="G100" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:55.791</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1779421857775</v>
-      </c>
-      <c r="C101" t="n">
-        <v>86023</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-12.13</v>
-      </c>
-      <c r="E101" t="n">
-        <v>83</v>
-      </c>
-      <c r="F101" t="n">
-        <v>745</v>
-      </c>
-      <c r="G101" t="n">
-        <v>39.31</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:55.792</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>1779421857977</v>
-      </c>
-      <c r="C102" t="n">
-        <v>86150</v>
-      </c>
-      <c r="D102" t="n">
-        <v>115.47</v>
-      </c>
-      <c r="E102" t="n">
-        <v>81</v>
-      </c>
-      <c r="F102" t="n">
-        <v>786</v>
-      </c>
-      <c r="G102" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:56.184</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>1779421858178</v>
-      </c>
-      <c r="C103" t="n">
-        <v>85745</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-295.3</v>
-      </c>
-      <c r="E103" t="n">
-        <v>81</v>
-      </c>
-      <c r="F103" t="n">
-        <v>786</v>
-      </c>
-      <c r="G103" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:56.184</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>1779421858379</v>
-      </c>
-      <c r="C104" t="n">
-        <v>85926</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-99.53</v>
-      </c>
-      <c r="E104" t="n">
-        <v>81</v>
-      </c>
-      <c r="F104" t="n">
-        <v>786</v>
-      </c>
-      <c r="G104" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:56.586</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>1779421858581</v>
-      </c>
-      <c r="C105" t="n">
-        <v>86146</v>
-      </c>
-      <c r="D105" t="n">
-        <v>125.44</v>
-      </c>
-      <c r="E105" t="n">
-        <v>80</v>
-      </c>
-      <c r="F105" t="n">
-        <v>684</v>
-      </c>
-      <c r="G105" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:56.587</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>1779421858782</v>
-      </c>
-      <c r="C106" t="n">
-        <v>85707</v>
-      </c>
-      <c r="D106" t="n">
-        <v>-319.83</v>
-      </c>
-      <c r="E106" t="n">
-        <v>80</v>
-      </c>
-      <c r="F106" t="n">
-        <v>684</v>
-      </c>
-      <c r="G106" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:56.994</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>1779421858984</v>
-      </c>
-      <c r="C107" t="n">
-        <v>85830</v>
-      </c>
-      <c r="D107" t="n">
-        <v>-180.84</v>
-      </c>
-      <c r="E107" t="n">
-        <v>80</v>
-      </c>
-      <c r="F107" t="n">
-        <v>684</v>
-      </c>
-      <c r="G107" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:56.995</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>1779421859185</v>
-      </c>
-      <c r="C108" t="n">
-        <v>86005</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E108" t="n">
-        <v>80</v>
-      </c>
-      <c r="F108" t="n">
-        <v>684</v>
-      </c>
-      <c r="G108" t="n">
-        <v>44.18</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:57.403</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>1779421859386</v>
-      </c>
-      <c r="C109" t="n">
-        <v>86206</v>
-      </c>
-      <c r="D109" t="n">
-        <v>204.04</v>
-      </c>
-      <c r="E109" t="n">
-        <v>80</v>
-      </c>
-      <c r="F109" t="n">
-        <v>766</v>
-      </c>
-      <c r="G109" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:57.403</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>1779421859588</v>
-      </c>
-      <c r="C110" t="n">
-        <v>85658</v>
-      </c>
-      <c r="D110" t="n">
-        <v>-354.16</v>
-      </c>
-      <c r="E110" t="n">
-        <v>80</v>
-      </c>
-      <c r="F110" t="n">
-        <v>766</v>
-      </c>
-      <c r="G110" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:57.859</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>1779421859789</v>
-      </c>
-      <c r="C111" t="n">
-        <v>85853</v>
-      </c>
-      <c r="D111" t="n">
-        <v>-141.45</v>
-      </c>
-      <c r="E111" t="n">
-        <v>80</v>
-      </c>
-      <c r="F111" t="n">
-        <v>766</v>
-      </c>
-      <c r="G111" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:57.859</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>1779421859991</v>
-      </c>
-      <c r="C112" t="n">
-        <v>86026</v>
-      </c>
-      <c r="D112" t="n">
-        <v>38.62</v>
-      </c>
-      <c r="E112" t="n">
-        <v>80</v>
-      </c>
-      <c r="F112" t="n">
-        <v>766</v>
-      </c>
-      <c r="G112" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:58.239</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>1779421860192</v>
-      </c>
-      <c r="C113" t="n">
-        <v>86224</v>
-      </c>
-      <c r="D113" t="n">
-        <v>234.69</v>
-      </c>
-      <c r="E113" t="n">
-        <v>79</v>
-      </c>
-      <c r="F113" t="n">
-        <v>765</v>
-      </c>
-      <c r="G113" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:58.240</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>1779421860394</v>
-      </c>
-      <c r="C114" t="n">
-        <v>85652</v>
-      </c>
-      <c r="D114" t="n">
-        <v>-349.04</v>
-      </c>
-      <c r="E114" t="n">
-        <v>79</v>
-      </c>
-      <c r="F114" t="n">
-        <v>765</v>
-      </c>
-      <c r="G114" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:58.632</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>1779421860595</v>
-      </c>
-      <c r="C115" t="n">
-        <v>85859</v>
-      </c>
-      <c r="D115" t="n">
-        <v>-124.59</v>
-      </c>
-      <c r="E115" t="n">
-        <v>79</v>
-      </c>
-      <c r="F115" t="n">
-        <v>765</v>
-      </c>
-      <c r="G115" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:58.633</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>1779421860796</v>
-      </c>
-      <c r="C116" t="n">
-        <v>86040</v>
-      </c>
-      <c r="D116" t="n">
-        <v>62.64</v>
-      </c>
-      <c r="E116" t="n">
-        <v>79</v>
-      </c>
-      <c r="F116" t="n">
-        <v>765</v>
-      </c>
-      <c r="G116" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:59.531</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>1779421860998</v>
-      </c>
-      <c r="C117" t="n">
-        <v>86185</v>
-      </c>
-      <c r="D117" t="n">
-        <v>204.51</v>
-      </c>
-      <c r="E117" t="n">
-        <v>79</v>
-      </c>
-      <c r="F117" t="n">
-        <v>786</v>
-      </c>
-      <c r="G117" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:59.532</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1779421861199</v>
-      </c>
-      <c r="C118" t="n">
-        <v>85742</v>
-      </c>
-      <c r="D118" t="n">
-        <v>-248.72</v>
-      </c>
-      <c r="E118" t="n">
-        <v>79</v>
-      </c>
-      <c r="F118" t="n">
-        <v>786</v>
-      </c>
-      <c r="G118" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:59.533</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>1779421861401</v>
-      </c>
-      <c r="C119" t="n">
-        <v>85946</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-32.28</v>
-      </c>
-      <c r="E119" t="n">
-        <v>79</v>
-      </c>
-      <c r="F119" t="n">
-        <v>786</v>
-      </c>
-      <c r="G119" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:59.534</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>1779421861602</v>
-      </c>
-      <c r="C120" t="n">
-        <v>86187</v>
-      </c>
-      <c r="D120" t="n">
-        <v>210.33</v>
-      </c>
-      <c r="E120" t="n">
-        <v>79</v>
-      </c>
-      <c r="F120" t="n">
-        <v>705</v>
-      </c>
-      <c r="G120" t="n">
-        <v>43.86</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:59.906</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>1779421861803</v>
-      </c>
-      <c r="C121" t="n">
-        <v>85846</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-141.19</v>
-      </c>
-      <c r="E121" t="n">
-        <v>79</v>
-      </c>
-      <c r="F121" t="n">
-        <v>705</v>
-      </c>
-      <c r="G121" t="n">
-        <v>43.86</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:50:59.906</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1779421862005</v>
-      </c>
-      <c r="C122" t="n">
-        <v>85883</v>
-      </c>
-      <c r="D122" t="n">
-        <v>-97.13</v>
-      </c>
-      <c r="E122" t="n">
-        <v>79</v>
-      </c>
-      <c r="F122" t="n">
-        <v>705</v>
-      </c>
-      <c r="G122" t="n">
-        <v>43.86</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:00.317</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>1779421862206</v>
-      </c>
-      <c r="C123" t="n">
-        <v>86029</v>
-      </c>
-      <c r="D123" t="n">
-        <v>53.73</v>
-      </c>
-      <c r="E123" t="n">
-        <v>79</v>
-      </c>
-      <c r="F123" t="n">
-        <v>705</v>
-      </c>
-      <c r="G123" t="n">
-        <v>43.86</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:00.317</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>1779421862408</v>
-      </c>
-      <c r="C124" t="n">
-        <v>86205</v>
-      </c>
-      <c r="D124" t="n">
-        <v>227.04</v>
-      </c>
-      <c r="E124" t="n">
-        <v>79</v>
-      </c>
-      <c r="F124" t="n">
-        <v>765</v>
-      </c>
-      <c r="G124" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:00.750</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1779421862609</v>
-      </c>
-      <c r="C125" t="n">
-        <v>85666</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-323.31</v>
-      </c>
-      <c r="E125" t="n">
-        <v>79</v>
-      </c>
-      <c r="F125" t="n">
-        <v>765</v>
-      </c>
-      <c r="G125" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:00.750</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>1779421862810</v>
-      </c>
-      <c r="C126" t="n">
-        <v>85850</v>
-      </c>
-      <c r="D126" t="n">
-        <v>-123.14</v>
-      </c>
-      <c r="E126" t="n">
-        <v>79</v>
-      </c>
-      <c r="F126" t="n">
-        <v>765</v>
-      </c>
-      <c r="G126" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:01.138</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>1779421863012</v>
-      </c>
-      <c r="C127" t="n">
-        <v>85994</v>
-      </c>
-      <c r="D127" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="E127" t="n">
-        <v>79</v>
-      </c>
-      <c r="F127" t="n">
-        <v>765</v>
-      </c>
-      <c r="G127" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:01.142</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>1779421863213</v>
-      </c>
-      <c r="C128" t="n">
-        <v>86174</v>
-      </c>
-      <c r="D128" t="n">
-        <v>205.66</v>
-      </c>
-      <c r="E128" t="n">
-        <v>78</v>
-      </c>
-      <c r="F128" t="n">
-        <v>786</v>
-      </c>
-      <c r="G128" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:01.703</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>1779421863415</v>
-      </c>
-      <c r="C129" t="n">
-        <v>85672</v>
-      </c>
-      <c r="D129" t="n">
-        <v>-306.62</v>
-      </c>
-      <c r="E129" t="n">
-        <v>78</v>
-      </c>
-      <c r="F129" t="n">
-        <v>786</v>
-      </c>
-      <c r="G129" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:01.703</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>1779421863616</v>
-      </c>
-      <c r="C130" t="n">
-        <v>85853</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-110.29</v>
-      </c>
-      <c r="E130" t="n">
-        <v>78</v>
-      </c>
-      <c r="F130" t="n">
-        <v>786</v>
-      </c>
-      <c r="G130" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:01.704</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>1779421863818</v>
-      </c>
-      <c r="C131" t="n">
-        <v>86053</v>
-      </c>
-      <c r="D131" t="n">
-        <v>95.23</v>
-      </c>
-      <c r="E131" t="n">
-        <v>81</v>
-      </c>
-      <c r="F131" t="n">
-        <v>705</v>
-      </c>
-      <c r="G131" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:02.114</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>1779421864019</v>
-      </c>
-      <c r="C132" t="n">
-        <v>85609</v>
-      </c>
-      <c r="D132" t="n">
-        <v>-353.54</v>
-      </c>
-      <c r="E132" t="n">
-        <v>81</v>
-      </c>
-      <c r="F132" t="n">
-        <v>705</v>
-      </c>
-      <c r="G132" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:02.115</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1779421864220</v>
-      </c>
-      <c r="C133" t="n">
-        <v>85823</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-121.86</v>
-      </c>
-      <c r="E133" t="n">
-        <v>81</v>
-      </c>
-      <c r="F133" t="n">
-        <v>705</v>
-      </c>
-      <c r="G133" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:02.525</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1779421864422</v>
-      </c>
-      <c r="C134" t="n">
-        <v>85991</v>
-      </c>
-      <c r="D134" t="n">
-        <v>52.23</v>
-      </c>
-      <c r="E134" t="n">
-        <v>81</v>
-      </c>
-      <c r="F134" t="n">
-        <v>705</v>
-      </c>
-      <c r="G134" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:02.525</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1779421864623</v>
-      </c>
-      <c r="C135" t="n">
-        <v>86231</v>
-      </c>
-      <c r="D135" t="n">
-        <v>289.62</v>
-      </c>
-      <c r="E135" t="n">
-        <v>82</v>
-      </c>
-      <c r="F135" t="n">
-        <v>664</v>
-      </c>
-      <c r="G135" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:02.940</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>1779421864825</v>
-      </c>
-      <c r="C136" t="n">
-        <v>85649</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-306.86</v>
-      </c>
-      <c r="E136" t="n">
-        <v>82</v>
-      </c>
-      <c r="F136" t="n">
-        <v>664</v>
-      </c>
-      <c r="G136" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:02.941</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>1779421865026</v>
-      </c>
-      <c r="C137" t="n">
-        <v>85854</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-86.52</v>
-      </c>
-      <c r="E137" t="n">
-        <v>82</v>
-      </c>
-      <c r="F137" t="n">
-        <v>664</v>
-      </c>
-      <c r="G137" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:03.352</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>1779421865227</v>
-      </c>
-      <c r="C138" t="n">
-        <v>86097</v>
-      </c>
-      <c r="D138" t="n">
-        <v>160.81</v>
-      </c>
-      <c r="E138" t="n">
-        <v>82</v>
-      </c>
-      <c r="F138" t="n">
-        <v>745</v>
-      </c>
-      <c r="G138" t="n">
-        <v>44.05</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:03.352</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1779421865429</v>
-      </c>
-      <c r="C139" t="n">
-        <v>86208</v>
-      </c>
-      <c r="D139" t="n">
-        <v>263.77</v>
-      </c>
-      <c r="E139" t="n">
-        <v>82</v>
-      </c>
-      <c r="F139" t="n">
-        <v>745</v>
-      </c>
-      <c r="G139" t="n">
-        <v>44.05</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:03.353</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1779421865630</v>
-      </c>
-      <c r="C140" t="n">
-        <v>85708</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-249.42</v>
-      </c>
-      <c r="E140" t="n">
-        <v>82</v>
-      </c>
-      <c r="F140" t="n">
-        <v>745</v>
-      </c>
-      <c r="G140" t="n">
-        <v>44.05</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:03.759</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1779421865832</v>
-      </c>
-      <c r="C141" t="n">
-        <v>85920</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-24.95</v>
-      </c>
-      <c r="E141" t="n">
-        <v>82</v>
-      </c>
-      <c r="F141" t="n">
-        <v>745</v>
-      </c>
-      <c r="G141" t="n">
-        <v>44.05</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:03.760</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779421866033</v>
-      </c>
-      <c r="C142" t="n">
-        <v>86150</v>
-      </c>
-      <c r="D142" t="n">
-        <v>206.3</v>
-      </c>
-      <c r="E142" t="n">
-        <v>82</v>
-      </c>
-      <c r="F142" t="n">
-        <v>786</v>
-      </c>
-      <c r="G142" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:04.162</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779421866234</v>
-      </c>
-      <c r="C143" t="n">
-        <v>86314</v>
-      </c>
-      <c r="D143" t="n">
-        <v>359.98</v>
-      </c>
-      <c r="E143" t="n">
-        <v>82</v>
-      </c>
-      <c r="F143" t="n">
-        <v>786</v>
-      </c>
-      <c r="G143" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:04.163</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779421866436</v>
-      </c>
-      <c r="C144" t="n">
-        <v>85743</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-229.01</v>
-      </c>
-      <c r="E144" t="n">
-        <v>82</v>
-      </c>
-      <c r="F144" t="n">
-        <v>786</v>
-      </c>
-      <c r="G144" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:04.690</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779421866637</v>
-      </c>
-      <c r="C145" t="n">
-        <v>85951</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-9.56</v>
-      </c>
-      <c r="E145" t="n">
-        <v>82</v>
-      </c>
-      <c r="F145" t="n">
-        <v>786</v>
-      </c>
-      <c r="G145" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:04.691</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779421866839</v>
-      </c>
-      <c r="C146" t="n">
-        <v>86133</v>
-      </c>
-      <c r="D146" t="n">
-        <v>172.91</v>
-      </c>
-      <c r="E146" t="n">
-        <v>79</v>
-      </c>
-      <c r="F146" t="n">
-        <v>826</v>
-      </c>
-      <c r="G146" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:05.126</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779421867040</v>
-      </c>
-      <c r="C147" t="n">
-        <v>85927</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-41.73</v>
-      </c>
-      <c r="E147" t="n">
-        <v>79</v>
-      </c>
-      <c r="F147" t="n">
-        <v>826</v>
-      </c>
-      <c r="G147" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:05.146</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779421867241</v>
-      </c>
-      <c r="C148" t="n">
-        <v>85888</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-78.65000000000001</v>
-      </c>
-      <c r="E148" t="n">
-        <v>79</v>
-      </c>
-      <c r="F148" t="n">
-        <v>826</v>
-      </c>
-      <c r="G148" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:05.413</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779421867443</v>
-      </c>
-      <c r="C149" t="n">
-        <v>86066</v>
-      </c>
-      <c r="D149" t="n">
-        <v>103.29</v>
-      </c>
-      <c r="E149" t="n">
-        <v>79</v>
-      </c>
-      <c r="F149" t="n">
-        <v>826</v>
-      </c>
-      <c r="G149" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:05.413</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779421867644</v>
-      </c>
-      <c r="C150" t="n">
-        <v>86278</v>
-      </c>
-      <c r="D150" t="n">
-        <v>310.12</v>
-      </c>
-      <c r="E150" t="n">
-        <v>78</v>
-      </c>
-      <c r="F150" t="n">
-        <v>705</v>
-      </c>
-      <c r="G150" t="n">
-        <v>50.89</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:05.817</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779421867846</v>
-      </c>
-      <c r="C151" t="n">
-        <v>85767</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-216.38</v>
-      </c>
-      <c r="E151" t="n">
-        <v>78</v>
-      </c>
-      <c r="F151" t="n">
-        <v>705</v>
-      </c>
-      <c r="G151" t="n">
-        <v>50.89</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:05.818</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779421868047</v>
-      </c>
-      <c r="C152" t="n">
-        <v>85956</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-16.56</v>
-      </c>
-      <c r="E152" t="n">
-        <v>78</v>
-      </c>
-      <c r="F152" t="n">
-        <v>705</v>
-      </c>
-      <c r="G152" t="n">
-        <v>50.89</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:51:06.222</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1779421868249</v>
-      </c>
-      <c r="C153" t="n">
-        <v>86119</v>
-      </c>
-      <c r="D153" t="n">
-        <v>147.26</v>
-      </c>
-      <c r="E153" t="n">
-        <v>78</v>
-      </c>
-      <c r="F153" t="n">
-        <v>705</v>
-      </c>
-      <c r="G153" t="n">
-        <v>50.89</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I97" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>12870</v>
+      </c>
+      <c r="L97" t="n">
+        <v>107</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.708</v>
       </c>
     </row>
   </sheetData>
